--- a/2-EXCEL/previsoes_completas_2026-01-01.xlsx
+++ b/2-EXCEL/previsoes_completas_2026-01-01.xlsx
@@ -704,7 +704,7 @@
         <v>1905</v>
       </c>
       <c r="I10" t="str">
-        <v>01/01/2026, 18:23:48</v>
+        <v>01/01/2026, 19:08:57</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         <v>1905</v>
       </c>
       <c r="I11" t="str">
-        <v>01/01/2026, 18:23:48</v>
+        <v>01/01/2026, 19:08:57</v>
       </c>
     </row>
     <row r="12">
@@ -762,7 +762,7 @@
         <v>1905</v>
       </c>
       <c r="I12" t="str">
-        <v>01/01/2026, 18:23:48</v>
+        <v>01/01/2026, 19:08:57</v>
       </c>
     </row>
     <row r="13">
@@ -791,7 +791,7 @@
         <v>1905</v>
       </c>
       <c r="I13" t="str">
-        <v>01/01/2026, 18:23:48</v>
+        <v>01/01/2026, 19:08:57</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +866,7 @@
         <v>1816</v>
       </c>
       <c r="E2" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="3">
@@ -883,7 +883,7 @@
         <v>1902</v>
       </c>
       <c r="E3" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="4">
@@ -900,7 +900,7 @@
         <v>1902</v>
       </c>
       <c r="E4" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="5">
@@ -917,7 +917,7 @@
         <v>1902</v>
       </c>
       <c r="E5" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="6">
@@ -934,7 +934,7 @@
         <v>1900</v>
       </c>
       <c r="E6" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="7">
@@ -951,7 +951,7 @@
         <v>1902</v>
       </c>
       <c r="E7" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
         <v>1906</v>
       </c>
       <c r="E8" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:57</v>
       </c>
     </row>
     <row r="9">
@@ -985,7 +985,7 @@
         <v>1902</v>
       </c>
       <c r="E9" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
         <v>1887</v>
       </c>
       <c r="E10" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="11">
@@ -1019,7 +1019,7 @@
         <v>1902</v>
       </c>
       <c r="E11" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         <v>1902</v>
       </c>
       <c r="E12" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="13">
@@ -1053,7 +1053,7 @@
         <v>1857</v>
       </c>
       <c r="E13" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="14">
@@ -1070,7 +1070,7 @@
         <v>1902</v>
       </c>
       <c r="E14" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:57</v>
       </c>
     </row>
     <row r="15">
@@ -1087,7 +1087,7 @@
         <v>1902</v>
       </c>
       <c r="E15" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="16">
@@ -1104,7 +1104,7 @@
         <v>1902</v>
       </c>
       <c r="E16" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="17">
@@ -1121,7 +1121,7 @@
         <v>1902</v>
       </c>
       <c r="E17" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="18">
@@ -1138,7 +1138,7 @@
         <v>1906</v>
       </c>
       <c r="E18" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:57</v>
       </c>
     </row>
     <row r="19">
@@ -1155,7 +1155,7 @@
         <v>1902</v>
       </c>
       <c r="E19" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="20">
@@ -1172,7 +1172,7 @@
         <v>1902</v>
       </c>
       <c r="E20" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="21">
@@ -1189,7 +1189,7 @@
         <v>1902</v>
       </c>
       <c r="E21" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="22">
@@ -1206,7 +1206,7 @@
         <v>1902</v>
       </c>
       <c r="E22" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="23">
@@ -1223,7 +1223,7 @@
         <v>1902</v>
       </c>
       <c r="E23" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:57</v>
       </c>
     </row>
     <row r="24">
@@ -1240,7 +1240,7 @@
         <v>1902</v>
       </c>
       <c r="E24" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="25">
@@ -1257,7 +1257,7 @@
         <v>1902</v>
       </c>
       <c r="E25" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="26">
@@ -1274,7 +1274,7 @@
         <v>1902</v>
       </c>
       <c r="E26" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="27">
@@ -1291,7 +1291,7 @@
         <v>1857</v>
       </c>
       <c r="E27" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="28">
@@ -1308,7 +1308,7 @@
         <v>1906</v>
       </c>
       <c r="E28" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:57</v>
       </c>
     </row>
     <row r="29">
@@ -1325,7 +1325,7 @@
         <v>1902</v>
       </c>
       <c r="E29" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="30">
@@ -1342,7 +1342,7 @@
         <v>1906</v>
       </c>
       <c r="E30" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:57</v>
       </c>
     </row>
     <row r="31">
@@ -1359,7 +1359,7 @@
         <v>1906</v>
       </c>
       <c r="E31" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="32">
@@ -1376,7 +1376,7 @@
         <v>1902</v>
       </c>
       <c r="E32" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="33">
@@ -1393,7 +1393,7 @@
         <v>1906</v>
       </c>
       <c r="E33" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="34">
@@ -1410,7 +1410,7 @@
         <v>1857</v>
       </c>
       <c r="E34" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="35">
@@ -1427,7 +1427,7 @@
         <v>1902</v>
       </c>
       <c r="E35" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="36">
@@ -1444,7 +1444,7 @@
         <v>1905</v>
       </c>
       <c r="E36" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="37">
@@ -1461,7 +1461,7 @@
         <v>1905</v>
       </c>
       <c r="E37" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="38">
@@ -1478,7 +1478,7 @@
         <v>1902</v>
       </c>
       <c r="E38" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="39">
@@ -1495,7 +1495,7 @@
         <v>1902</v>
       </c>
       <c r="E39" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="40">
@@ -1512,7 +1512,7 @@
         <v>1902</v>
       </c>
       <c r="E40" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="41">
@@ -1529,7 +1529,7 @@
         <v>1905</v>
       </c>
       <c r="E41" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="42">
@@ -1546,7 +1546,7 @@
         <v>1902</v>
       </c>
       <c r="E42" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="43">
@@ -1563,7 +1563,7 @@
         <v>1905</v>
       </c>
       <c r="E43" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="44">
@@ -1580,7 +1580,7 @@
         <v>1902</v>
       </c>
       <c r="E44" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="45">
@@ -1597,7 +1597,7 @@
         <v>1902</v>
       </c>
       <c r="E45" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="46">
@@ -1614,7 +1614,7 @@
         <v>1900</v>
       </c>
       <c r="E46" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="47">
@@ -1631,7 +1631,7 @@
         <v>1906</v>
       </c>
       <c r="E47" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="48">
@@ -1648,7 +1648,7 @@
         <v>1902</v>
       </c>
       <c r="E48" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="49">
@@ -1665,7 +1665,7 @@
         <v>1902</v>
       </c>
       <c r="E49" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="50">
@@ -1682,7 +1682,7 @@
         <v>1902</v>
       </c>
       <c r="E50" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="51">
@@ -1699,7 +1699,7 @@
         <v>1902</v>
       </c>
       <c r="E51" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="52">
@@ -1716,7 +1716,7 @@
         <v>1857</v>
       </c>
       <c r="E52" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="53">
@@ -1733,7 +1733,7 @@
         <v>1902</v>
       </c>
       <c r="E53" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="54">
@@ -1750,7 +1750,7 @@
         <v>1902</v>
       </c>
       <c r="E54" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="55">
@@ -1767,7 +1767,7 @@
         <v>1887</v>
       </c>
       <c r="E55" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="56">
@@ -1784,7 +1784,7 @@
         <v>1902</v>
       </c>
       <c r="E56" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="57">
@@ -1801,7 +1801,7 @@
         <v>1906</v>
       </c>
       <c r="E57" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="58">
@@ -1818,7 +1818,7 @@
         <v>1902</v>
       </c>
       <c r="E58" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="59">
@@ -1835,7 +1835,7 @@
         <v>1900</v>
       </c>
       <c r="E59" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="60">
@@ -1852,7 +1852,7 @@
         <v>1902</v>
       </c>
       <c r="E60" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="61">
@@ -1869,7 +1869,7 @@
         <v>1902</v>
       </c>
       <c r="E61" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
     <row r="62">
@@ -1886,7 +1886,7 @@
         <v>1902</v>
       </c>
       <c r="E62" t="str">
-        <v>01/01/2026, 18:23:50</v>
+        <v>01/01/2026, 19:08:59</v>
       </c>
     </row>
     <row r="63">
@@ -1903,7 +1903,7 @@
         <v>1816</v>
       </c>
       <c r="E63" t="str">
-        <v>01/01/2026, 18:23:49</v>
+        <v>01/01/2026, 19:08:58</v>
       </c>
     </row>
   </sheetData>
